--- a/Back to Home.xlsx
+++ b/Back to Home.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9420" activeTab="4"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9420" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="操作方法" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="86">
   <si>
     <t>Back to Home</t>
     <phoneticPr fontId="1"/>
@@ -107,16 +107,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>凍った床</t>
-    <rPh sb="0" eb="1">
-      <t>コオ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ユカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>疲労回復</t>
     <rPh sb="0" eb="4">
       <t>ヒロウカイフク</t>
@@ -363,13 +353,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>すべりやすい床</t>
-    <rPh sb="6" eb="7">
-      <t>ユカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>森の敵</t>
     <rPh sb="0" eb="1">
       <t>モリ</t>
@@ -684,6 +667,52 @@
     <rPh sb="1" eb="3">
       <t>ゾウカ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステータス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大まかな流れ</t>
+    <rPh sb="0" eb="1">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ナガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↓</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ１（アルファ）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ２（ベータ）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↓</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ３（ベータ）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↓</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エンディング（ベータ）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトル（アルファ）</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1084,7 +1113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -1119,33 +1148,38 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16">
         <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" t="s">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1156,37 +1190,85 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>28</v>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="L5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="L6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="L7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="L8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="L9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="L10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="L11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="L12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="L13" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1208,21 +1290,21 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2" t="s">
         <v>52</v>
       </c>
-      <c r="K2" t="s">
-        <v>54</v>
-      </c>
       <c r="L2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -1233,7 +1315,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="I4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J4">
         <v>7</v>
@@ -1244,13 +1326,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -1259,12 +1341,12 @@
         <v>30</v>
       </c>
       <c r="L5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="I6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J6">
         <v>5</v>
@@ -1273,15 +1355,15 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1292,7 +1374,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="I8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J8">
         <v>12</v>
@@ -1303,10 +1385,10 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J9">
         <v>20</v>
@@ -1315,15 +1397,15 @@
         <v>10</v>
       </c>
       <c r="L9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J11">
         <v>10</v>
@@ -1332,12 +1414,12 @@
         <v>50</v>
       </c>
       <c r="L11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="I12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J12">
         <v>15</v>
@@ -1346,24 +1428,24 @@
         <v>80</v>
       </c>
       <c r="L12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
         <v>43</v>
       </c>
-      <c r="B13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" t="s">
-        <v>45</v>
-      </c>
       <c r="I13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J13">
         <v>25</v>
@@ -1374,41 +1456,41 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" t="s">
         <v>48</v>
-      </c>
-      <c r="B21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1420,12 +1502,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
@@ -1435,7 +1517,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
@@ -1445,7 +1527,7 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
@@ -1455,17 +1537,7 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1481,92 +1553,92 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
       <c r="G5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
         <v>18</v>
       </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
       <c r="G9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
         <v>21</v>
       </c>
-      <c r="C13" t="s">
-        <v>22</v>
-      </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
         <v>23</v>
       </c>
-      <c r="C15" t="s">
-        <v>24</v>
-      </c>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G15" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
         <v>25</v>
       </c>
-      <c r="C17" t="s">
-        <v>26</v>
-      </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/Back to Home.xlsx
+++ b/Back to Home.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA2B\Desktop\BackHome\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA2B\Desktop\Team\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9420" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9420" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="操作方法" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="83">
   <si>
     <t>Back to Home</t>
     <phoneticPr fontId="1"/>
@@ -367,10 +367,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>オオカミ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>BOSS</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -390,10 +386,6 @@
   </si>
   <si>
     <t>コウモリ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>スケルトン</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -469,10 +461,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>スケルトン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>特殊効果</t>
     <rPh sb="0" eb="4">
       <t>トクシュコウカ</t>
@@ -511,22 +499,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>１回復活する（２秒後に復活）</t>
-    <rPh sb="1" eb="2">
-      <t>カイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>フッカツ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ビョウゴ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>フッカツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>雑魚スライムを召喚</t>
     <rPh sb="0" eb="2">
       <t>ザコ</t>
@@ -713,6 +685,19 @@
   </si>
   <si>
     <t>タイトル（アルファ）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃すると壊れる箱</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>コワ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ハコ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1114,30 +1099,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="5" spans="1:5" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:5" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="5" spans="1:5" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:5" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:5" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -1148,35 +1133,35 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C15">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -1191,84 +1176,84 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="L5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="L6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="L7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="L8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="L9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="L10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="L11" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="L7" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="L12" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="L8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="L9" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="L13" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="L10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="L11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="L12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="L13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1281,25 +1266,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="J2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K2" t="s">
         <v>50</v>
       </c>
-      <c r="K2" t="s">
-        <v>52</v>
-      </c>
       <c r="L2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -1313,9 +1298,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="I4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J4">
         <v>7</v>
@@ -1324,15 +1309,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>36</v>
       </c>
-      <c r="B5" t="s">
-        <v>37</v>
-      </c>
       <c r="I5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -1341,71 +1323,59 @@
         <v>30</v>
       </c>
       <c r="L5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="I6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" t="s">
         <v>55</v>
       </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>15</v>
-      </c>
-      <c r="L6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="I8" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
+        <v>10</v>
+      </c>
+      <c r="L8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
         <v>38</v>
       </c>
-      <c r="I7" t="s">
-        <v>43</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="I8" t="s">
-        <v>58</v>
-      </c>
-      <c r="J8">
-        <v>12</v>
-      </c>
-      <c r="K8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
         <v>39</v>
       </c>
-      <c r="I9" t="s">
-        <v>59</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>10</v>
-      </c>
-      <c r="L9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
       <c r="I11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J11">
         <v>10</v>
@@ -1414,12 +1384,12 @@
         <v>50</v>
       </c>
       <c r="L11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="I12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J12">
         <v>15</v>
@@ -1428,24 +1398,21 @@
         <v>80</v>
       </c>
       <c r="L12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J13">
         <v>25</v>
@@ -1454,43 +1421,43 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" t="s">
-        <v>46</v>
       </c>
       <c r="B21" t="s">
         <v>36</v>
       </c>
       <c r="C21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
         <v>47</v>
-      </c>
-      <c r="D21" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1502,42 +1469,47 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1549,19 +1521,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1569,10 +1541,10 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1580,10 +1552,10 @@
         <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1591,15 +1563,15 @@
         <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1607,13 +1579,13 @@
         <v>21</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -1621,13 +1593,13 @@
         <v>23</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1635,10 +1607,10 @@
         <v>25</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/Back to Home.xlsx
+++ b/Back to Home.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9420" activeTab="3"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9420" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="操作方法" sheetId="1" r:id="rId1"/>
@@ -483,22 +483,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>負の効果を薬草に付与</t>
-    <rPh sb="0" eb="1">
-      <t>フ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ヤクソウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>フヨ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>雑魚スライムを召喚</t>
     <rPh sb="0" eb="2">
       <t>ザコ</t>
@@ -697,6 +681,13 @@
     </rPh>
     <rPh sb="8" eb="9">
       <t>ハコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デバフ付与</t>
+    <rPh sb="3" eb="5">
+      <t>フヨ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1133,7 +1124,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
@@ -1143,12 +1134,12 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
@@ -1188,7 +1179,7 @@
         <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
@@ -1198,47 +1189,47 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="L5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="L6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="L7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="L8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="L9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="L10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="L11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="L12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="L13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
@@ -1253,7 +1244,7 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1323,7 +1314,7 @@
         <v>30</v>
       </c>
       <c r="L5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
@@ -1362,7 +1353,7 @@
         <v>10</v>
       </c>
       <c r="L8" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
@@ -1384,7 +1375,7 @@
         <v>50</v>
       </c>
       <c r="L11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.4">
@@ -1398,7 +1389,7 @@
         <v>80</v>
       </c>
       <c r="L12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.4">
@@ -1509,7 +1500,7 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1541,7 +1532,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
@@ -1552,7 +1543,7 @@
         <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
@@ -1563,7 +1554,7 @@
         <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
@@ -1579,10 +1570,10 @@
         <v>21</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
@@ -1593,10 +1584,10 @@
         <v>23</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
@@ -1607,10 +1598,10 @@
         <v>25</v>
       </c>
       <c r="F17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/Back to Home.xlsx
+++ b/Back to Home.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9420" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9420" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="操作方法" sheetId="1" r:id="rId1"/>
@@ -483,6 +483,22 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>負の効果を薬草に付与</t>
+    <rPh sb="0" eb="1">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヤクソウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>雑魚スライムを召喚</t>
     <rPh sb="0" eb="2">
       <t>ザコ</t>
@@ -681,13 +697,6 @@
     </rPh>
     <rPh sb="8" eb="9">
       <t>ハコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>デバフ付与</t>
-    <rPh sb="3" eb="5">
-      <t>フヨ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1124,7 +1133,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
@@ -1134,12 +1143,12 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
@@ -1179,7 +1188,7 @@
         <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
@@ -1189,47 +1198,47 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="L5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="L6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="L7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="L8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="L9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="L10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="L11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="L12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="L13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
@@ -1244,7 +1253,7 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1314,7 +1323,7 @@
         <v>30</v>
       </c>
       <c r="L5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
@@ -1353,7 +1362,7 @@
         <v>10</v>
       </c>
       <c r="L8" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
@@ -1375,7 +1384,7 @@
         <v>50</v>
       </c>
       <c r="L11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.4">
@@ -1389,7 +1398,7 @@
         <v>80</v>
       </c>
       <c r="L12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.4">
@@ -1500,7 +1509,7 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1541,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
@@ -1543,7 +1552,7 @@
         <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
@@ -1554,7 +1563,7 @@
         <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
@@ -1570,10 +1579,10 @@
         <v>21</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
@@ -1584,10 +1593,10 @@
         <v>23</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
@@ -1598,10 +1607,10 @@
         <v>25</v>
       </c>
       <c r="F17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/Back to Home.xlsx
+++ b/Back to Home.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9420" activeTab="3"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9420" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="操作方法" sheetId="1" r:id="rId1"/>
@@ -28,11 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="83">
-  <si>
-    <t>Back to Home</t>
-    <phoneticPr fontId="1"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="81">
   <si>
     <t>操作方法</t>
     <rPh sb="0" eb="4">
@@ -41,22 +37,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>W</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>A</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>S</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>D</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ステージ概要</t>
     <rPh sb="4" eb="6">
       <t>ガイヨウ</t>
@@ -301,10 +281,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>スペースでジャンプ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>マップ内に落ちている松明を使用して通れるようにする</t>
     <rPh sb="3" eb="4">
       <t>ナイ</t>
@@ -601,16 +577,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>マウスで剣を振る</t>
-    <rPh sb="4" eb="5">
-      <t>ケン</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>フ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>移動</t>
     <rPh sb="0" eb="2">
       <t>イドウ</t>
@@ -642,10 +608,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ステータス</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>大まかな流れ</t>
     <rPh sb="0" eb="1">
       <t>オオ</t>
@@ -698,6 +660,36 @@
     <rPh sb="8" eb="9">
       <t>ハコ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WASD</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Space</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マウス左クリック</t>
+    <rPh sb="3" eb="4">
+      <t>ヒダリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーステータス</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -730,27 +722,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -759,15 +736,24 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -784,55 +770,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>5129</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>58270</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>238304</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="972283"/>
-          <a:ext cx="4879385" cy="2651059"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1098,73 +1035,155 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="8.625" customWidth="1"/>
+    <col min="1" max="1" width="8.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="1"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L33"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="5" spans="1:5" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="L5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="L6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="L7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="L8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="L9" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="L10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="L11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="L12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="L13" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16">
-        <v>100</v>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1173,123 +1192,33 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="L5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="L6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="L7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="L8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="L9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="L10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="L11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="L12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="L13" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
-        <v>69</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="K2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="L2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -1298,9 +1227,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="I4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="J4">
         <v>7</v>
@@ -1309,12 +1238,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -1323,12 +1252,12 @@
         <v>30</v>
       </c>
       <c r="L5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="I6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1337,12 +1266,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I7" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="J7">
         <v>12</v>
@@ -1351,9 +1280,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="I8" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J8">
         <v>20</v>
@@ -1362,20 +1291,20 @@
         <v>10</v>
       </c>
       <c r="L8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="I11" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="J11">
         <v>10</v>
@@ -1384,12 +1313,12 @@
         <v>50</v>
       </c>
       <c r="L11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="I12" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J12">
         <v>15</v>
@@ -1398,21 +1327,21 @@
         <v>80</v>
       </c>
       <c r="L12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" t="s">
         <v>41</v>
-      </c>
-      <c r="I13" t="s">
-        <v>47</v>
       </c>
       <c r="J13">
         <v>25</v>
@@ -1421,43 +1350,43 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1470,46 +1399,46 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A12"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1521,96 +1450,96 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="C9" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+      <c r="G9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
         <v>15</v>
       </c>
-      <c r="G5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="C13" t="s">
         <v>16</v>
       </c>
-      <c r="G7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
+      <c r="F13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
         <v>17</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C15" t="s">
         <v>18</v>
       </c>
-      <c r="G9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
+      <c r="F15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
+      <c r="C17" t="s">
         <v>20</v>
       </c>
-      <c r="C13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" t="s">
-        <v>61</v>
-      </c>
-      <c r="G13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" t="s">
-        <v>25</v>
-      </c>
       <c r="F17" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G17" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Back to Home.xlsx
+++ b/Back to Home.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9420" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9420"/>
   </bookViews>
   <sheets>
     <sheet name="操作方法" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="81">
   <si>
     <t>操作方法</t>
     <rPh sb="0" eb="4">
@@ -383,10 +383,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ゴブリン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>オオカミ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -404,13 +400,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>保留</t>
-    <rPh sb="0" eb="2">
-      <t>ホリュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>攻撃力</t>
     <rPh sb="0" eb="3">
       <t>コウゲキリョク</t>
@@ -437,13 +426,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>特殊効果</t>
-    <rPh sb="0" eb="4">
-      <t>トクシュコウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>洞窟ボス</t>
     <rPh sb="0" eb="2">
       <t>ドウクツ</t>
@@ -451,81 +433,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ゴブリン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>クサ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>負の効果を薬草に付与</t>
-    <rPh sb="0" eb="1">
-      <t>フ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ヤクソウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>フヨ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>雑魚スライムを召喚</t>
-    <rPh sb="0" eb="2">
-      <t>ザコ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ショウカン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>発熱効果を薬草に付与（１５秒）</t>
-    <rPh sb="0" eb="2">
-      <t>ハツネツ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ヤクソウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>フヨ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ビョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>発熱効果＋疲労増加を薬草に付与（３０秒）</t>
-    <rPh sb="0" eb="2">
-      <t>ハツネツ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ヒロウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ゾウカ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヤクソウ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>フヨ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ビョウ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -690,6 +598,65 @@
   </si>
   <si>
     <t>プレイヤーステータス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>山ボス</t>
+    <rPh sb="0" eb="1">
+      <t>ヤマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オオカKING</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EXP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弾丸を発射</t>
+    <rPh sb="0" eb="2">
+      <t>ダンガン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハッシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メモ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一番弱い敵</t>
+    <rPh sb="0" eb="2">
+      <t>イチバン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヨワ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>少しだけ動く</t>
+    <rPh sb="0" eb="1">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>突進してくる</t>
+    <rPh sb="0" eb="2">
+      <t>トッシン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1051,46 +1018,46 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B10">
         <v>100</v>
@@ -1118,7 +1085,7 @@
         <v>21</v>
       </c>
       <c r="L3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1128,47 +1095,47 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="L5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="L6" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="L7" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="L8" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="L9" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="L10" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="L11" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="L12" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="L13" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
@@ -1183,7 +1150,7 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1194,26 +1161,32 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="14" max="14" width="39" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="J2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" t="s">
         <v>42</v>
       </c>
-      <c r="K2" t="s">
-        <v>44</v>
-      </c>
       <c r="L2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>75</v>
+      </c>
+      <c r="N2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1221,172 +1194,179 @@
         <v>30</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="L3">
+        <v>10</v>
+      </c>
+      <c r="N3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="I4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>25</v>
+      </c>
+      <c r="L4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>30</v>
       </c>
       <c r="I5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>25</v>
+      </c>
+      <c r="L5">
+        <v>30</v>
+      </c>
+      <c r="N5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="I6" t="s">
         <v>46</v>
       </c>
-      <c r="J5">
+      <c r="J6">
         <v>10</v>
       </c>
-      <c r="K5">
-        <v>30</v>
-      </c>
-      <c r="L5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="I6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
       <c r="K6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <v>50</v>
+      </c>
+      <c r="N6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>31</v>
       </c>
       <c r="I7" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="J7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K7">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="I8" t="s">
-        <v>50</v>
-      </c>
-      <c r="J8">
-        <v>20</v>
-      </c>
-      <c r="K8">
-        <v>10</v>
-      </c>
-      <c r="L8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="L7">
+        <v>45</v>
+      </c>
+      <c r="N7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9">
+        <v>10</v>
+      </c>
+      <c r="K9">
+        <v>45</v>
+      </c>
+      <c r="L9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="I10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10">
+        <v>7</v>
+      </c>
+      <c r="K10">
+        <v>65</v>
+      </c>
+      <c r="L10">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>33</v>
       </c>
       <c r="I11" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="J11">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K11">
-        <v>50</v>
-      </c>
-      <c r="L11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="I12" t="s">
-        <v>48</v>
-      </c>
-      <c r="J12">
-        <v>15</v>
-      </c>
-      <c r="K12">
-        <v>80</v>
-      </c>
-      <c r="L12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>90</v>
+      </c>
+      <c r="L11">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" t="s">
         <v>35</v>
       </c>
-      <c r="I13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J13">
-        <v>25</v>
-      </c>
-      <c r="K13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" t="s">
         <v>38</v>
-      </c>
-      <c r="B21" t="s">
-        <v>30</v>
       </c>
       <c r="C21" t="s">
         <v>39</v>
       </c>
-      <c r="D21" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1438,7 +1418,7 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1470,7 +1450,7 @@
         <v>10</v>
       </c>
       <c r="G5" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1481,7 +1461,7 @@
         <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1492,7 +1472,7 @@
         <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1508,10 +1488,10 @@
         <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G13" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1522,10 +1502,10 @@
         <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G15" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1536,10 +1516,10 @@
         <v>20</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G17" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
